--- a/平台部署时间进度表_6月8日-20日.xlsx
+++ b/平台部署时间进度表_6月8日-20日.xlsx
@@ -594,10 +594,11 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>统计时间：2026年6月5日 | 总模块：16个 | 已完成：11个 | 进行中：2个 | 待开始：2个 | 等待备案：1个</t>
-        </is>
-      </c>
-    </row>
+          <t>统计时间：2026年6月12日 ｜ 总模块：16个 ｜ 已完成：14个 ｜ 进行中：1个 ｜ 待开始：1个 ｜ 等待备案：0个</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -930,12 +931,12 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>🔄 进行中</t>
+          <t>✔ 已完成</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>预计6月6日</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -945,7 +946,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>客户可修改检测到的尺寸</t>
+          <t>商户后台可修改红框尺寸</t>
         </is>
       </c>
     </row>
@@ -957,12 +958,12 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>🔄 进行中</t>
+          <t>✔ 已完成</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>预计6月6日</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -972,7 +973,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>查看投诉列表、处理投诉</t>
+          <t>投诉列表+详情处理完整实现</t>
         </is>
       </c>
     </row>
@@ -984,12 +985,12 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>⏸ 等待审核</t>
+          <t>✔ 已通过</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>预计6月8日</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -999,7 +1000,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>备案审核中，预计6月8日通过</t>
+          <t>已上线 www.zhibanhome.com</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1012,12 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>⏳ 待开始</t>
+          <t>🔄 进行中</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>6月10日-11日</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1026,7 +1027,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>SQLite数据迁移</t>
+          <t>服务器已升级4核8G，具备迁移条件</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1044,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>6月12日-13日</t>
+          <t>预计6月15-16日</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1057,6 +1058,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
@@ -1133,7 +1135,8 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>已完成
+ECS已升级4核8G，OSS/SSL/Nginx已就绪</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1177,8 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>确认服务器资源充足</t>
+          <t>进行中
+服务器升级完成，开始迁移</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1218,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>保留SQLite作为回退备份</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1259,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>使用Certbot免费证书</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1299,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>周末安排值班人员</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>优先级：阻断性 &gt; 一般</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>准备上线检查清单</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1450,6 +1454,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1490,7 +1495,8 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>低
+已完成（ECS 4核8G + OSS 100G/年）</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1518,8 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高
+进行中，预计6月13-14日</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1541,8 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中
+预计6月15-16日</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1564,8 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高
+预计6月17-19日</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1587,8 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高
+预计6月20日</t>
         </is>
       </c>
     </row>
